--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42112,7 +42112,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45382,7 +45382,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1565,6 +1565,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1713,6 +1718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2305,6 +2325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2453,6 +2478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2601,6 +2631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3541,6 +3576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3851,6 +3891,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3999,6 +4044,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4147,6 +4197,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4295,6 +4350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4443,6 +4503,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4984,6 +5049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5132,6 +5202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5280,6 +5355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5428,6 +5508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5576,6 +5661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7305,6 +7395,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7453,6 +7548,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7601,6 +7701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7749,6 +7854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7897,6 +8007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8045,6 +8160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8193,6 +8313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8737,6 +8862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9047,6 +9177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9195,6 +9330,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9343,6 +9483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9491,6 +9636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9639,6 +9789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9787,6 +9942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9935,6 +10095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10476,6 +10641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10624,6 +10794,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10772,6 +10947,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10920,6 +11100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11068,6 +11253,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12797,6 +12987,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13093,6 +13288,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13241,6 +13441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13389,6 +13594,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13537,6 +13747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13833,6 +14048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13981,6 +14201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14129,6 +14354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15069,6 +15299,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15379,6 +15614,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15527,6 +15767,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15675,6 +15920,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15971,6 +16221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16119,6 +16374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16267,6 +16527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16808,6 +17073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16956,6 +17226,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17104,6 +17379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17252,6 +17532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17400,6 +17685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17548,6 +17838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19271,6 +19566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19416,6 +19716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19561,6 +19866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19706,6 +20016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19851,6 +20166,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19996,6 +20316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20141,6 +20466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20286,6 +20616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21376,6 +21711,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21521,6 +21861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21666,6 +22011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21811,6 +22161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21956,6 +22311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22494,6 +22854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22639,6 +23004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22784,6 +23154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22929,6 +23304,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23074,6 +23454,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24791,6 +25176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25081,6 +25471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25226,6 +25621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25516,6 +25916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25661,6 +26066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25806,6 +26216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26737,6 +27152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27041,6 +27461,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27186,6 +27611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27331,6 +27761,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27476,6 +27911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27621,6 +28061,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27766,6 +28211,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27911,6 +28361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28449,6 +28904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28594,6 +29054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28739,6 +29204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28884,6 +29354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29029,6 +29504,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29174,6 +29654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31326,6 +31811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31761,6 +32251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31906,6 +32401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32196,6 +32696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32341,6 +32846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32486,6 +32996,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33024,6 +33539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33562,6 +34082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33707,6 +34232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33852,6 +34382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33997,6 +34532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34142,6 +34682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34680,6 +35225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34825,6 +35375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34970,6 +35525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35115,6 +35675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35260,6 +35825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35405,6 +35975,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37122,6 +37697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37412,6 +37992,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37847,6 +38432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37992,6 +38582,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38282,6 +38877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38427,6 +39027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38572,6 +39177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39110,6 +39720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39648,6 +40263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39793,6 +40413,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39938,6 +40563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40083,6 +40713,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40228,6 +40863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40766,6 +41406,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40911,6 +41556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41056,6 +41706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41201,6 +41856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41346,6 +42006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43063,6 +43728,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43498,6 +44168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43643,6 +44318,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43788,6 +44468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44719,6 +45404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44864,6 +45554,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45009,6 +45704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45547,6 +46247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45692,6 +46397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45837,6 +46547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45980,6 +46695,11 @@
       <c r="S274" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22689,7 +22689,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24618,7 +24618,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26987,7 +26987,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28739,7 +28739,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -30032,7 +30032,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31501,7 +31501,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33374,7 +33374,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36353,7 +36353,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -37139,7 +37139,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -37532,7 +37532,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39555,7 +39555,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -41241,7 +41241,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42777,7 +42777,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -43170,7 +43170,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -43563,7 +43563,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44846,7 +44846,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -46082,7 +46082,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -47075,7 +47075,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -47468,7 +47468,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
